--- a/jogos_2025-02-12.xlsx
+++ b/jogos_2025-02-12.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adanaspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>5.25</v>
+        <v>4.06</v>
       </c>
       <c r="O2" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="X2" t="n">
-        <v>3.72</v>
+        <v>2.46</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['17', '55', '90+2']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '77']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45700.33333333334</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Adanaspor</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>4.06</v>
+        <v>5.25</v>
       </c>
       <c r="O3" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
-        <v>2.46</v>
+        <v>3.72</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['17', '55', '90+2']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['1', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45700.33333333334</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.14</v>
+        <v>3.3</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.67</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['46', '52', '76']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['22', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.75</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.14</v>
+        <v>2.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45700.41666666666</v>
@@ -1030,109 +1030,109 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EGS Gafsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>1.14</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
-        <v>2.05</v>
+        <v>15</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>1.67</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
+        <v>13</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA5" t="n">
         <v>2.75</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>9.1</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
         <v>2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46', '52', '76']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['22', '81']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.21</v>
+        <v>4.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.25</v>
+        <v>1.14</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.67</v>
+        <v>8.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45700.41666666666</v>
@@ -1159,20 +1159,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>EGS Gafsa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="M6" t="n">
         <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
         <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="S6" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.8</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.83</v>
-      </c>
       <c r="Y6" t="n">
-        <v>3.09</v>
+        <v>2.84</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.85</v>
+        <v>9.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45700.41666666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['47', '87']</t>
+          <t>['62', '89']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45700.45833333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.97</v>
+        <v>2.84</v>
       </c>
       <c r="M9" t="n">
-        <v>3.21</v>
+        <v>2.79</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['47', '87']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['48', '68', '88']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AI9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45700.45833333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['62', '89']</t>
+          <t>['48', '68', '88']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45700.45833333334</v>
@@ -1804,23 +1804,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enyimba</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
@@ -1830,65 +1830,65 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>4.75</v>
+        <v>3.68</v>
       </c>
       <c r="U11" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>1.97</v>
+        <v>2.36</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AA11" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.95</v>
+        <v>2.37</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['22', '57']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" t="n">
         <v>1.53</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45700.5</v>
@@ -1933,91 +1933,91 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Enyimba</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.28</v>
-      </c>
       <c r="T12" t="n">
-        <v>3.68</v>
+        <v>4.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="X12" t="n">
-        <v>2.36</v>
+        <v>1.97</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.37</v>
+        <v>2.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['22', '57']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AI12" t="n">
         <v>1.53</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45700.5</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,19 +2191,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="O14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.6</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.82</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['10', '90']</t>
+          <t>['8', '83', '90+8']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.45</v>
+        <v>4.75</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45700.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>2.87</v>
       </c>
       <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.22</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '90']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG15" t="n">
         <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45700.58333333334</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.29</v>
+        <v>2.28</v>
       </c>
       <c r="M16" t="n">
-        <v>4.8</v>
+        <v>2.86</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.73</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['8', '83', '90+8']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45700.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O17" t="n">
         <v>4</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>8.65</v>
-      </c>
-      <c r="M17" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '90+4']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['4', '25', '68', '78']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45700.61458333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.66</v>
+        <v>8.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.63</v>
+        <v>5.06</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>1.3</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="P18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AA18" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['15', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['4', '25', '68', '78']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45700.61458333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,16 +3094,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -3120,65 +3120,65 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="M21" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
         <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.75</v>
+        <v>5.35</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['11', '73']</t>
+          <t>['27', '60', '90']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45700.69791666666</v>
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.34</v>
+        <v>1.57</v>
       </c>
       <c r="M22" t="n">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="N22" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="X22" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['3', '21']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>3.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['66']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45700.69791666666</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3367,76 +3367,76 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="N23" t="n">
-        <v>6</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['3', '21']</t>
+          <t>['11', '73']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45700.69791666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,16 +3481,16 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -3507,65 +3507,65 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.3</v>
       </c>
-      <c r="S24" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['27', '60', '90']</t>
+          <t>['13', '58']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45700.69791666666</v>
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.64</v>
+        <v>2.34</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
         <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
         <v>1.4</v>
@@ -3789,19 +3789,19 @@
         <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
         <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X26" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Y26" t="n">
         <v>1.87</v>
@@ -3810,38 +3810,38 @@
         <v>1.87</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['13', '58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AH26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45700.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,16 +3868,16 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -3886,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>2.22</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="O27" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R27" t="n">
         <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
         <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['32', '75', '87']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.67</v>
       </c>
-      <c r="AH27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45700.70833333334</v>
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['47', '63']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>2.88</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['32', '75', '87']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45700.70833333334</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
         <v>2.8</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z29" t="n">
         <v>1.62</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>4</v>
-      </c>
-      <c r="U29" t="n">
+      <c r="AA29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.22</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="AC29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.57</v>
       </c>
-      <c r="X29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45700.70833333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,19 +4255,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.67</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>2.89</v>
       </c>
       <c r="O30" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="P30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z30" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="AA30" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.44</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4344,20 +4344,20 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['47', '63']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45700.70833333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.73</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['45+7']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['45+6']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45700.70833333334</v>
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="M32" t="n">
-        <v>3.67</v>
+        <v>5.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.89</v>
+        <v>1.37</v>
       </c>
       <c r="O32" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="P32" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.44</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.65</v>
-      </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.89</v>
+        <v>2.01</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['45', '49']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.41</v>
+        <v>3.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.58</v>
+        <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.73</v>
+        <v>3.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45700.70833333334</v>
@@ -4632,35 +4632,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>7.8</v>
+        <v>2.8</v>
       </c>
       <c r="M33" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>1.37</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="P33" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
         <v>1.22</v>
       </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.73</v>
-      </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>1.57</v>
       </c>
       <c r="X33" t="n">
-        <v>6.8</v>
+        <v>2.35</v>
       </c>
       <c r="Y33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z33" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z33" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AA33" t="n">
-        <v>2.01</v>
+        <v>5.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.81</v>
+        <v>1.13</v>
       </c>
       <c r="AC33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD33" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['45', '49']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AI33" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45700.70833333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,19 +4771,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -4797,80 +4797,80 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.61</v>
+        <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="O34" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P34" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.88</v>
       </c>
-      <c r="R34" t="n">
+      <c r="U34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.33</v>
       </c>
-      <c r="S34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AI34" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AJ34" t="n">
         <v>1.73</v>
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="O35" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P35" t="n">
         <v>2.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="R35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U35" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.36</v>
       </c>
       <c r="V35" t="n">
         <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X35" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC35" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+7']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+6']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AI35" t="n">
         <v>1.57</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45700.70833333334</v>
